--- a/notebooks/Ale/feature_importance_por_sector_full_data.xlsx
+++ b/notebooks/Ale/feature_importance_por_sector_full_data.xlsx
@@ -582,42 +582,44 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>0.1464</v>
+        <v>0.2632</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>0.3331</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>0.1147</v>
-      </c>
+        <v>0.3895</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="6" t="n">
-        <v>0.2928</v>
-      </c>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr"/>
       <c r="C8" s="9" t="n">
-        <v>0.2785</v>
+        <v>0.2466</v>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr"/>
@@ -625,88 +627,84 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>size_micro_share</t>
+          <t>cycle_to_employer</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="6" t="n">
-        <v>0.2635</v>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="6" t="n">
+        <v>0.1441</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.2299</v>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>0.2553</v>
-      </c>
+          <t>related_variety</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr"/>
       <c r="C10" s="9" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>0.1485</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>0.149</v>
-      </c>
+        <v>0.1903</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0.2009</v>
-      </c>
+          <t>within_sector_diversity</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr"/>
       <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
+      <c r="D11" s="6" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0.1817</v>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>within_sector_diversity</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr"/>
       <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="9" t="n">
-        <v>0.113</v>
-      </c>
+      <c r="D12" s="7" t="inlineStr"/>
       <c r="E12" s="9" t="n">
-        <v>0.1817</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>cycle_to_employer</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr"/>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0.1552</v>
+      </c>
       <c r="C13" s="7" t="inlineStr"/>
       <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="6" t="n">
-        <v>0.1476</v>
-      </c>
+      <c r="E13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>transport_to_employer</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr"/>
       <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="9" t="n">
-        <v>0.1389</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
+        <v>0.1373</v>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -717,7 +715,7 @@
       <c r="B15" s="7" t="inlineStr"/>
       <c r="C15" s="7" t="inlineStr"/>
       <c r="D15" s="6" t="n">
-        <v>0.1305</v>
+        <v>0.1148</v>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
     </row>
@@ -743,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -797,14 +795,12 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>0.2578</v>
-      </c>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr"/>
       <c r="C5" s="6" t="n">
-        <v>0.4402</v>
+        <v>0.6246</v>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr"/>
@@ -812,40 +808,40 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>within_sector_diversity</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr"/>
-      <c r="C6" s="7" t="inlineStr"/>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>0.4218</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>0.09379999999999999</v>
+      </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="9" t="n">
-        <v>0.4197</v>
-      </c>
+      <c r="E6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>transport_to_employer</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>0.3248</v>
-      </c>
+          <t>within_sector_diversity</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr"/>
       <c r="C7" s="7" t="inlineStr"/>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
+      <c r="E7" s="6" t="n">
+        <v>0.4197</v>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>0.322</v>
-      </c>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr"/>
       <c r="C8" s="9" t="n">
-        <v>0.3065</v>
+        <v>0.407</v>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr"/>
@@ -872,24 +868,22 @@
       <c r="B10" s="7" t="inlineStr"/>
       <c r="C10" s="7" t="inlineStr"/>
       <c r="D10" s="9" t="n">
-        <v>0.2879</v>
+        <v>0.2223</v>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr"/>
       <c r="C11" s="7" t="inlineStr"/>
       <c r="D11" s="6" t="n">
-        <v>0.09429999999999999</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0.226</v>
-      </c>
+        <v>0.1748</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -901,52 +895,80 @@
       <c r="C12" s="7" t="inlineStr"/>
       <c r="D12" s="7" t="inlineStr"/>
       <c r="E12" s="9" t="n">
-        <v>0.2191</v>
+        <v>0.1717</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>0.1953</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>0.1193</v>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="6" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.1583</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr"/>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>0.1575</v>
+      </c>
       <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="9" t="n">
-        <v>0.1422</v>
-      </c>
+      <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>housing_net_additions</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr"/>
       <c r="C15" s="7" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="6" t="n">
-        <v>0.1004</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="D15" s="6" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>0.1419</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="6" t="n">
+        <v>0.1031</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Sin datos para classification en este sector</t>
         </is>
@@ -967,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1020,11 +1042,11 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.455</v>
+        <v>0.4518</v>
       </c>
       <c r="C5" s="7" t="inlineStr"/>
       <c r="D5" s="6" t="n">
-        <v>0.1827</v>
+        <v>0.1664</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -1033,49 +1055,51 @@
           <t>broadband</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr"/>
+      <c r="B6" s="9" t="n">
+        <v>0.1706</v>
+      </c>
       <c r="C6" s="9" t="n">
-        <v>0.3637</v>
+        <v>0.3636</v>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="6" t="n">
-        <v>0.2684</v>
-      </c>
+      <c r="C7" s="7" t="inlineStr"/>
       <c r="D7" s="6" t="n">
-        <v>0.1246</v>
+        <v>0.3504</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr"/>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="9" t="n">
-        <v>0.2626</v>
-      </c>
+      <c r="C8" s="9" t="n">
+        <v>0.2422</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr"/>
       <c r="C9" s="6" t="n">
-        <v>0.1245</v>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
+        <v>0.2374</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.1069</v>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -1084,7 +1108,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.1231</v>
+        <v>0.2066</v>
       </c>
       <c r="C10" s="7" t="inlineStr"/>
       <c r="D10" s="7" t="inlineStr"/>
@@ -1092,17 +1116,41 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="C11" s="7" t="inlineStr"/>
+          <t>n_universities_feecap_lad</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="6" t="n">
+        <v>0.1374</v>
+      </c>
       <c r="D11" s="7" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>unemployment_rate</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr"/>
+      <c r="C12" s="7" t="inlineStr"/>
+      <c r="D12" s="9" t="n">
+        <v>0.1318</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>transport_to_employer</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Sin datos para classification en este sector</t>
         </is>
@@ -1190,74 +1238,72 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>0.3423</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>0.2596</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
+        <v>0.4584</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="9" t="n">
+        <v>0.2648</v>
+      </c>
       <c r="E6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>0.2461</v>
-      </c>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="6" t="n">
-        <v>0.3322</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>0.2321</v>
-      </c>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>n_universities_feecap_lad</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr"/>
-      <c r="C8" s="9" t="n">
-        <v>0.2724</v>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="9" t="n">
+        <v>0.2291</v>
+      </c>
       <c r="E8" s="9" t="n">
-        <v>0.1249</v>
+        <v>0.3534</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>fe_participation</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>0.1767</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.29</v>
+      </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="6" t="n">
-        <v>0.2325</v>
-      </c>
+      <c r="E9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>size_micro_share</t>
+          <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr"/>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="9" t="n">
-        <v>0.2303</v>
-      </c>
+      <c r="C10" s="9" t="n">
+        <v>0.2565</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -1276,37 +1322,39 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="9" t="n">
-        <v>0.1918</v>
-      </c>
+      <c r="C12" s="7" t="inlineStr"/>
       <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr"/>
+      <c r="E12" s="9" t="n">
+        <v>0.1891</v>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr"/>
       <c r="C13" s="7" t="inlineStr"/>
       <c r="D13" s="6" t="n">
-        <v>0.1537</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr"/>
+        <v>0.1234</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.1597</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.1082</v>
+        <v>0.1433</v>
       </c>
       <c r="C14" s="7" t="inlineStr"/>
       <c r="D14" s="7" t="inlineStr"/>
@@ -1315,15 +1363,13 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>0.0975</v>
-      </c>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr"/>
       <c r="C15" s="7" t="inlineStr"/>
       <c r="D15" s="6" t="n">
-        <v>0.0881</v>
+        <v>0.1253</v>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
     </row>
@@ -1416,18 +1462,16 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>n_universities_feecap_lad</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>0.3185</v>
+        <v>0.5002</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>0.3752</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>0.1892</v>
-      </c>
+        <v>0.504</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -1436,109 +1480,115 @@
           <t>related_variety</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>0.12</v>
-      </c>
+      <c r="B7" s="7" t="inlineStr"/>
       <c r="C7" s="6" t="n">
-        <v>0.343</v>
+        <v>0.1934</v>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
       <c r="E7" s="6" t="n">
-        <v>0.3526</v>
+        <v>0.3038</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>within_sector_diversity</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr"/>
       <c r="C8" s="9" t="n">
-        <v>0.2629</v>
+        <v>0.2845</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.1206</v>
+        <v>0.1239</v>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>enterprise_birth_rate</t>
+          <t>within_sector_diversity</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="6" t="n">
-        <v>0.1832</v>
-      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>broadband</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr"/>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>0.2151</v>
+      </c>
       <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="9" t="n">
-        <v>0.1216</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="9" t="n">
+        <v>0.1268</v>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr"/>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0.0747</v>
+      </c>
       <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="6" t="n">
-        <v>0.0949</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="6" t="n">
+        <v>0.1705</v>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>size_micro_share</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>0.0898</v>
-      </c>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr"/>
       <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="7" t="inlineStr"/>
+      <c r="D12" s="9" t="n">
+        <v>0.1358</v>
+      </c>
       <c r="E12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>0.08740000000000001</v>
-      </c>
-      <c r="C13" s="7" t="inlineStr"/>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.0649</v>
+      </c>
       <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
+      <c r="E13" s="6" t="n">
+        <v>0.1287</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr"/>
       <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="9" t="n">
-        <v>0.0755</v>
-      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1631,76 +1681,78 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr"/>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>0.1511</v>
+      </c>
       <c r="C6" s="9" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
+        <v>0.4286</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0.1237</v>
+      </c>
       <c r="E6" s="9" t="n">
-        <v>0.384</v>
+        <v>0.0968</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.2008</v>
+        <v>0.1971</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.3355</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>0.1328</v>
-      </c>
+        <v>0.2777</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
       <c r="E7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>0.1754</v>
-      </c>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr"/>
       <c r="C8" s="9" t="n">
-        <v>0.2067</v>
+        <v>0.1255</v>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
+      <c r="E8" s="9" t="n">
+        <v>0.2536</v>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>0.1647</v>
-      </c>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr"/>
       <c r="C9" s="7" t="inlineStr"/>
       <c r="D9" s="6" t="n">
-        <v>0.1175</v>
+        <v>0.1274</v>
       </c>
       <c r="E9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>size_micro_share</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.1611</v>
+        <v>0.1192</v>
       </c>
       <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
+      <c r="D10" s="9" t="n">
+        <v>0.1255</v>
+      </c>
       <c r="E10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -1712,36 +1764,34 @@
       <c r="B11" s="7" t="inlineStr"/>
       <c r="C11" s="7" t="inlineStr"/>
       <c r="D11" s="6" t="n">
-        <v>0.1458</v>
+        <v>0.119</v>
       </c>
       <c r="E11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>enterprise_birth_rate</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr"/>
       <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="9" t="n">
-        <v>0.1184</v>
-      </c>
+      <c r="D12" s="7" t="inlineStr"/>
       <c r="E12" s="9" t="n">
-        <v>0.1055</v>
+        <v>0.1117</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>enterprise_birth_rate</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr"/>
       <c r="C13" s="7" t="inlineStr"/>
       <c r="D13" s="7" t="inlineStr"/>
       <c r="E13" s="6" t="n">
-        <v>0.0934</v>
+        <v>0.0902</v>
       </c>
     </row>
     <row r="16">
@@ -1766,7 +1816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1825,107 +1875,131 @@
       </c>
       <c r="B5" s="7" t="inlineStr"/>
       <c r="C5" s="6" t="n">
-        <v>0.4169</v>
+        <v>0.5142</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.1344</v>
+        <v>0.1218</v>
       </c>
       <c r="E5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>size_large_share</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>0.2286</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>0.2665</v>
-      </c>
+        <v>0.2534</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr"/>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="9" t="n">
-        <v>0.1537</v>
-      </c>
+      <c r="E6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>n_universities_feecap_lad</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.2639</v>
+        <v>0.249</v>
       </c>
       <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="6" t="n">
-        <v>0.1612</v>
-      </c>
+      <c r="D7" s="7" t="inlineStr"/>
       <c r="E7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>size_large_share</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>0.2534</v>
-      </c>
-      <c r="C8" s="7" t="inlineStr"/>
+        <v>0.2477</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0.1426</v>
+      </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
+      <c r="E8" s="9" t="n">
+        <v>0.1324</v>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.1752</v>
-      </c>
-      <c r="C9" s="7" t="inlineStr"/>
+        <v>0.1604</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.2452</v>
+      </c>
       <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="6" t="n">
-        <v>0.1507</v>
+        <v>0.1139</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>within_sector_diversity</t>
+          <t>enterprise_death_rate</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr"/>
-      <c r="C10" s="9" t="n">
-        <v>0.1349</v>
-      </c>
+      <c r="C10" s="7" t="inlineStr"/>
       <c r="D10" s="9" t="n">
-        <v>0.11</v>
+        <v>0.1406</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1631</v>
+        <v>0.1637</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>enterprise_death_rate</t>
+          <t>within_sector_diversity</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr"/>
       <c r="C11" s="7" t="inlineStr"/>
       <c r="D11" s="6" t="n">
-        <v>0.1447</v>
+        <v>0.11</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.135</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+        <v>0.1631</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr"/>
+      <c r="C12" s="9" t="n">
+        <v>0.1467</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="6" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Sin datos para classification en este sector</t>
         </is>
